--- a/complete_backend_solution/tests/component_data_TEST/avionics_TEST/TEST_avionics.xlsx
+++ b/complete_backend_solution/tests/component_data_TEST/avionics_TEST/TEST_avionics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felix\PycharmProjects\cubesat_component_matcher\complete_backend_solution\tests\component_data_TEST\avionics_TEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81115607-23B5-46F1-8A88-C04D850EA15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E8B54E0-E083-4232-9CA9-299ED7326EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{46C8D7D6-FD08-4204-9126-CA1B9C70BEEC}"/>
+    <workbookView xWindow="15825" yWindow="2895" windowWidth="16695" windowHeight="15345" xr2:uid="{46C8D7D6-FD08-4204-9126-CA1B9C70BEEC}"/>
   </bookViews>
   <sheets>
     <sheet name="boards" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Board</t>
   </si>
@@ -100,6 +100,12 @@
   </si>
   <si>
     <t>5-20</t>
+  </si>
+  <si>
+    <t>board 4</t>
+  </si>
+  <si>
+    <t>-10,-5,-2</t>
   </si>
 </sst>
 </file>
@@ -472,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00BD45A9-DE0D-44C9-9A20-641DB25CF74D}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -528,6 +534,17 @@
       </c>
       <c r="C5">
         <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>-5</v>
       </c>
     </row>
   </sheetData>
